--- a/linear-regression-data.xlsx
+++ b/linear-regression-data.xlsx
@@ -3150,10 +3150,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>161.46</c:v>
+                  <c:v>169.97941176470587</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>168.86</c:v>
+                  <c:v>160.34058823529418</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>170.96</c:v>
@@ -3312,10 +3312,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>54.05</c:v>
+                  <c:v>45.01745098039216</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52.5</c:v>
+                  <c:v>61.532549019607835</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>57.33</c:v>
@@ -12975,18 +12975,18 @@
     </row>
     <row r="2" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
-        <v>161.46</v>
+        <v>169.97941176470587</v>
       </c>
       <c r="B2" s="2">
-        <v>54.05</v>
+        <v>45.01745098039216</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
-        <v>168.86</v>
+        <v>160.34058823529418</v>
       </c>
       <c r="B3" s="2">
-        <v>52.5</v>
+        <v>61.532549019607835</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
